--- a/data/trans_orig/P62-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P62-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2007</t>
+          <t>Población según si percibe alguna pensión en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>42220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63499</t>
+          <t>62620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74620</t>
+          <t>74908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105717</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>44992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100547</t>
+          <t>101853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122186</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150749</t>
+          <t>151008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181846</t>
+          <t>181558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107758</t>
+          <t>107765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137431</t>
+          <t>137682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63665</t>
+          <t>64308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94230</t>
+          <t>96703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181732</t>
+          <t>180999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>225319</t>
+          <t>226374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114836</t>
+          <t>114829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>275085</t>
+          <t>272612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305650</t>
+          <t>305007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366590</t>
+          <t>365535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410177</t>
+          <t>410910</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>63072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88629</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52874</t>
+          <t>54449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81443</t>
+          <t>80725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124198</t>
+          <t>123323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160822</t>
+          <t>160881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54514</t>
+          <t>55773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78907</t>
+          <t>80071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159403</t>
+          <t>160121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187972</t>
+          <t>186397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>223166</t>
+          <t>223107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259790</t>
+          <t>260665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59024</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81084</t>
+          <t>80572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>51929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78425</t>
+          <t>78451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117696</t>
+          <t>117182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153296</t>
+          <t>154133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>75489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156946</t>
+          <t>156920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182526</t>
+          <t>183442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216219</t>
+          <t>215382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251819</t>
+          <t>252333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46247</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65537</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94996</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32337</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50124</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110995</t>
+          <t>111452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>131893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148936</t>
+          <t>148397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178395</t>
+          <t>177327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52771</t>
+          <t>52853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73431</t>
+          <t>73735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35837</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94936</t>
+          <t>92191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128685</t>
+          <t>126388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>39998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60962</t>
+          <t>60880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135358</t>
+          <t>133494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159490</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180375</t>
+          <t>182672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214124</t>
+          <t>216869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124864</t>
+          <t>126034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159185</t>
+          <t>160684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100758</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138327</t>
+          <t>138833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235162</t>
+          <t>238379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286948</t>
+          <t>286456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119081</t>
+          <t>117582</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153402</t>
+          <t>152232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318271</t>
+          <t>317765</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355840</t>
+          <t>358186</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>447916</t>
+          <t>448408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>499702</t>
+          <t>496485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152205</t>
+          <t>151617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183480</t>
+          <t>183320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111655</t>
+          <t>109259</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152775</t>
+          <t>150352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>268204</t>
+          <t>267877</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>327409</t>
+          <t>324842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>390213</t>
+          <t>392636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>431333</t>
+          <t>433729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>488740</t>
+          <t>491307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>547945</t>
+          <t>548272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>704703</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>777999</t>
+          <t>776905</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>538793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>619576</t>
+          <t>620420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1262052</t>
+          <t>1264825</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1379693</t>
+          <t>1381379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>581344</t>
+          <t>582438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>654640</t>
+          <t>653320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1726965</t>
+          <t>1726121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1811530</t>
+          <t>1807748</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2326190</t>
+          <t>2324504</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2443831</t>
+          <t>2441058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2012</t>
+          <t>Población según si percibe alguna pensión en 2012 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63108</t>
+          <t>63394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89378</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54408</t>
+          <t>55571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82896</t>
+          <t>83801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125572</t>
+          <t>125406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164704</t>
+          <t>164959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77571</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103841</t>
+          <t>103555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105133</t>
+          <t>104228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133621</t>
+          <t>132458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190274</t>
+          <t>190019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229406</t>
+          <t>229572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113923</t>
+          <t>114128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>151731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72142</t>
+          <t>74503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109427</t>
+          <t>109368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193309</t>
+          <t>197035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246695</t>
+          <t>252860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>177543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215351</t>
+          <t>215146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284158</t>
+          <t>284217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321443</t>
+          <t>319082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476165</t>
+          <t>470000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>529551</t>
+          <t>525825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67554</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95662</t>
+          <t>95496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>61260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91979</t>
+          <t>91024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137719</t>
+          <t>138540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176806</t>
+          <t>178628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84236</t>
+          <t>84402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112344</t>
+          <t>110675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164624</t>
+          <t>165579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>194808</t>
+          <t>195343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259695</t>
+          <t>257873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298782</t>
+          <t>297961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86605</t>
+          <t>88304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116449</t>
+          <t>117997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86670</t>
+          <t>86887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118936</t>
+          <t>117632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179319</t>
+          <t>183638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226076</t>
+          <t>228671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111968</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141812</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161690</t>
+          <t>162994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193956</t>
+          <t>193739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282967</t>
+          <t>280372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329724</t>
+          <t>325405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59930</t>
+          <t>60004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>81943</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112245</t>
+          <t>114793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67323</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90576</t>
+          <t>89824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102950</t>
+          <t>102876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126986</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179897</t>
+          <t>177349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212703</t>
+          <t>210199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62352</t>
+          <t>61807</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86742</t>
+          <t>86235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47376</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73930</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117488</t>
+          <t>115561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154171</t>
+          <t>153842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67936</t>
+          <t>68443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150809</t>
+          <t>149301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177363</t>
+          <t>176303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225246</t>
+          <t>225575</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261929</t>
+          <t>263856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140685</t>
+          <t>140721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180881</t>
+          <t>178181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129525</t>
+          <t>128765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172787</t>
+          <t>171394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>282660</t>
+          <t>277713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340724</t>
+          <t>342180</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201303</t>
+          <t>204003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241499</t>
+          <t>241463</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>334048</t>
+          <t>335441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377310</t>
+          <t>378070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>548295</t>
+          <t>546839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606359</t>
+          <t>611306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>173712</t>
+          <t>174044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217007</t>
+          <t>214432</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133716</t>
+          <t>132230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176716</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319144</t>
+          <t>319686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>382257</t>
+          <t>378899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>193743</t>
+          <t>196318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>237038</t>
+          <t>236706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>383526</t>
+          <t>382762</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>426526</t>
+          <t>428012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588735</t>
+          <t>592093</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>651848</t>
+          <t>651306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>822352</t>
+          <t>827419</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>917084</t>
+          <t>915256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>699546</t>
+          <t>705813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>792414</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1556186</t>
+          <t>1555651</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1691213</t>
+          <t>1682935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1064329</t>
+          <t>1066157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1159061</t>
+          <t>1153994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1781124</t>
+          <t>1777599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1873992</t>
+          <t>1867725</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2863739</t>
+          <t>2872017</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2998766</t>
+          <t>2999301</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2016</t>
+          <t>Población según si percibe alguna pensión en 2016 (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>46985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72063</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67427</t>
+          <t>68542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97199</t>
+          <t>95594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134428</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84738</t>
+          <t>85012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109093</t>
+          <t>109816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115762</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141990</t>
+          <t>139834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205562</t>
+          <t>208152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242791</t>
+          <t>244396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130795</t>
+          <t>130532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168175</t>
+          <t>167579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74296</t>
+          <t>75009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111143</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>214838</t>
+          <t>215154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266891</t>
+          <t>267229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159290</t>
+          <t>159886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196670</t>
+          <t>196933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297022</t>
+          <t>297315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333869</t>
+          <t>333156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468739</t>
+          <t>468401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>520792</t>
+          <t>520476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77222</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102837</t>
+          <t>102930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65438</t>
+          <t>65184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95011</t>
+          <t>95907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148919</t>
+          <t>150096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189453</t>
+          <t>191174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83143</t>
+          <t>83050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108758</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150743</t>
+          <t>149847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180316</t>
+          <t>180570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242281</t>
+          <t>240560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282815</t>
+          <t>281638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80791</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111918</t>
+          <t>111037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66022</t>
+          <t>66508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98312</t>
+          <t>99751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155163</t>
+          <t>156338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203332</t>
+          <t>198842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>140949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171195</t>
+          <t>171400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201016</t>
+          <t>199577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347982</t>
+          <t>352472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396151</t>
+          <t>394976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55517</t>
+          <t>55907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79464</t>
+          <t>78343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69516</t>
+          <t>69375</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109142</t>
+          <t>108499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140400</t>
+          <t>139706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>51948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74774</t>
+          <t>74384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92654</t>
+          <t>92795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117289</t>
+          <t>118138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152061</t>
+          <t>152755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183319</t>
+          <t>183962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61165</t>
+          <t>61823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85264</t>
+          <t>86332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98416</t>
+          <t>102561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135595</t>
+          <t>137620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70357</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94456</t>
+          <t>93798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134804</t>
+          <t>134981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160206</t>
+          <t>159453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212906</t>
+          <t>210881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250085</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>135201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171656</t>
+          <t>171006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>132473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173874</t>
+          <t>173491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281633</t>
+          <t>282486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335158</t>
+          <t>335719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121568</t>
+          <t>122218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156774</t>
+          <t>158023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223145</t>
+          <t>223528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>264546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>355085</t>
+          <t>354524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>408610</t>
+          <t>407757</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>191741</t>
+          <t>190924</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>234629</t>
+          <t>234361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153433</t>
+          <t>156100</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202259</t>
+          <t>203457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>361415</t>
+          <t>361080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>426153</t>
+          <t>426342</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>210320</t>
+          <t>210588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>253208</t>
+          <t>254025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>367512</t>
+          <t>366314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416338</t>
+          <t>413671</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588567</t>
+          <t>588378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>653305</t>
+          <t>653640</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>858465</t>
+          <t>857980</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>945068</t>
+          <t>945922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>695881</t>
+          <t>693930</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>792794</t>
+          <t>788550</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1583199</t>
+          <t>1575264</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1701824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1001248</t>
+          <t>1000394</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1087851</t>
+          <t>1088336</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1665482</t>
+          <t>1669726</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1762395</t>
+          <t>1764346</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2694261</t>
+          <t>2702769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2821394</t>
+          <t>2829329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2023</t>
+          <t>Población según si percibe alguna pensión en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39458</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67999</t>
+          <t>67792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82363</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100239</t>
+          <t>99363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105844</t>
+          <t>106111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120986</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193190</t>
+          <t>193397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>216914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>112546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156662</t>
+          <t>157882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108028</t>
+          <t>107931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138353</t>
+          <t>138054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231823</t>
+          <t>230554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>285318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112342</t>
+          <t>111122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157029</t>
+          <t>156458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>202803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232829</t>
+          <t>232926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325795</t>
+          <t>324543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>378038</t>
+          <t>379307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77465</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>104381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72281</t>
+          <t>72240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94192</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157953</t>
+          <t>158649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194040</t>
+          <t>192816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>62010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88926</t>
+          <t>87493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132884</t>
+          <t>131209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154795</t>
+          <t>154836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199427</t>
+          <t>200651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235514</t>
+          <t>234818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92650</t>
+          <t>92849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69271</t>
+          <t>69887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91870</t>
+          <t>91791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140844</t>
+          <t>141114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177003</t>
+          <t>177293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>50882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123138</t>
+          <t>123217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145737</t>
+          <t>145121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181735</t>
+          <t>181445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217894</t>
+          <t>217624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>35523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>63036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81676</t>
+          <t>82364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83248</t>
+          <t>82560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101194</t>
+          <t>101888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>68637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90975</t>
+          <t>91088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51200</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69354</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153461</t>
+          <t>152945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>65938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101300</t>
+          <t>102356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119454</t>
+          <t>120377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151768</t>
+          <t>152284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179167</t>
+          <t>180832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136770</t>
+          <t>137974</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179457</t>
+          <t>180210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223003</t>
+          <t>221618</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>466391</t>
+          <t>473614</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390341</t>
+          <t>392210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>687938</t>
+          <t>671417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109337</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152024</t>
+          <t>150820</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70839</t>
+          <t>63616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314227</t>
+          <t>315612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>138086</t>
+          <t>154607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>435683</t>
+          <t>433814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>181637</t>
+          <t>183041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219300</t>
+          <t>219081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159526</t>
+          <t>159640</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193453</t>
+          <t>192255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354963</t>
+          <t>354763</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>401141</t>
+          <t>402129</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78343</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116006</t>
+          <t>114602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>248103</t>
+          <t>249301</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>282030</t>
+          <t>281916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338058</t>
+          <t>337070</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384236</t>
+          <t>384436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>757945</t>
+          <t>757511</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>846187</t>
+          <t>850378</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>801281</t>
+          <t>803430</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1350692</t>
+          <t>1297233</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1612998</t>
+          <t>1614534</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2158940</t>
+          <t>2133061</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>634340</t>
+          <t>630149</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>722582</t>
+          <t>723016</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>827411</t>
+          <t>880870</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1376822</t>
+          <t>1374673</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1499690</t>
+          <t>1525569</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2045632</t>
+          <t>2044096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P62-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>47617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74908</t>
+          <t>74845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65392</t>
+          <t>65545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101853</t>
+          <t>101237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122940</t>
+          <t>121971</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151008</t>
+          <t>151983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181558</t>
+          <t>181621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107765</t>
+          <t>106948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137682</t>
+          <t>136645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64308</t>
+          <t>65611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96703</t>
+          <t>96430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>180213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226374</t>
+          <t>228739</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114829</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272612</t>
+          <t>272885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305007</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365535</t>
+          <t>363170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410910</t>
+          <t>411696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63072</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87370</t>
+          <t>87681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54449</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80725</t>
+          <t>81495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>125779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160881</t>
+          <t>162214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55773</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>79913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160121</t>
+          <t>159351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186397</t>
+          <t>187253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>223107</t>
+          <t>221774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260665</t>
+          <t>258209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80572</t>
+          <t>81127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51929</t>
+          <t>52855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78451</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117182</t>
+          <t>118763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154133</t>
+          <t>153127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53573</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75489</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156920</t>
+          <t>156586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183442</t>
+          <t>182516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215382</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252333</t>
+          <t>250752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>54742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>45856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66605</t>
+          <t>66312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95535</t>
+          <t>96086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111452</t>
+          <t>111386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131893</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148397</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177327</t>
+          <t>177620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>53303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73735</t>
+          <t>74468</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61833</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>94542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126388</t>
+          <t>127872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>60430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133494</t>
+          <t>134057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>159178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182672</t>
+          <t>181188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216869</t>
+          <t>214518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126034</t>
+          <t>127132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>160828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>101473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138833</t>
+          <t>137912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>238379</t>
+          <t>237742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286456</t>
+          <t>288591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117582</t>
+          <t>117438</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152232</t>
+          <t>151134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>317765</t>
+          <t>318686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>358186</t>
+          <t>355125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>448408</t>
+          <t>446273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>496485</t>
+          <t>497122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151617</t>
+          <t>151904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183320</t>
+          <t>184024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109259</t>
+          <t>107564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150352</t>
+          <t>148470</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>267877</t>
+          <t>269154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324842</t>
+          <t>323065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89841</t>
+          <t>89137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121544</t>
+          <t>121257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>392636</t>
+          <t>394518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>433729</t>
+          <t>435424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>491307</t>
+          <t>493084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>548272</t>
+          <t>546995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>704978</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>776905</t>
+          <t>776480</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>538793</t>
+          <t>536304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>620420</t>
+          <t>621544</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1264825</t>
+          <t>1267016</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1381379</t>
+          <t>1382544</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>582438</t>
+          <t>582863</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>653320</t>
+          <t>654365</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1726121</t>
+          <t>1724997</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1807748</t>
+          <t>1810237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2324504</t>
+          <t>2323339</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2441058</t>
+          <t>2438867</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63394</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91038</t>
+          <t>89082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55571</t>
+          <t>56270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>84766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125406</t>
+          <t>126659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164959</t>
+          <t>165298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>77867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103555</t>
+          <t>103875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>103263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132458</t>
+          <t>131759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190019</t>
+          <t>189680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229572</t>
+          <t>228319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114128</t>
+          <t>113881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151731</t>
+          <t>152255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>73174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>108717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197035</t>
+          <t>197966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252860</t>
+          <t>250721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177543</t>
+          <t>177019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215146</t>
+          <t>215393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284217</t>
+          <t>284868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>320411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470000</t>
+          <t>472139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525825</t>
+          <t>524894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69223</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95496</t>
+          <t>97967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61260</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91024</t>
+          <t>92255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138540</t>
+          <t>139234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178628</t>
+          <t>181011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84402</t>
+          <t>81931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110675</t>
+          <t>110954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165579</t>
+          <t>164348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195343</t>
+          <t>194710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257873</t>
+          <t>255490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297961</t>
+          <t>297267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117997</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86887</t>
+          <t>87125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117632</t>
+          <t>118367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183638</t>
+          <t>183108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228671</t>
+          <t>226415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110420</t>
+          <t>110104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140113</t>
+          <t>141718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193739</t>
+          <t>193501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280372</t>
+          <t>282628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325405</t>
+          <t>325935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62835</t>
+          <t>61571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>80373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>113170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>67691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>103149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177349</t>
+          <t>178972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210199</t>
+          <t>211769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,49%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61807</t>
+          <t>61233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86235</t>
+          <t>86346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48436</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75438</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115561</t>
+          <t>116504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153842</t>
+          <t>152762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92871</t>
+          <t>93445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149301</t>
+          <t>149546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>176032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225575</t>
+          <t>226655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263856</t>
+          <t>262913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140721</t>
+          <t>138815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178181</t>
+          <t>179775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128765</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171394</t>
+          <t>171440</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277713</t>
+          <t>282569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342180</t>
+          <t>342332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204003</t>
+          <t>202409</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241463</t>
+          <t>243369</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>335441</t>
+          <t>335395</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378070</t>
+          <t>376022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546839</t>
+          <t>546687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611306</t>
+          <t>606450</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174044</t>
+          <t>171910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>214432</t>
+          <t>215360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132230</t>
+          <t>133212</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177480</t>
+          <t>177789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319686</t>
+          <t>316112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>378899</t>
+          <t>381297</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196318</t>
+          <t>195390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>236706</t>
+          <t>238840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>382762</t>
+          <t>382453</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>428012</t>
+          <t>427030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>592093</t>
+          <t>589695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>651306</t>
+          <t>654880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>827419</t>
+          <t>827071</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>915256</t>
+          <t>916749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>705813</t>
+          <t>700539</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>795939</t>
+          <t>796120</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1555651</t>
+          <t>1557149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1682935</t>
+          <t>1690707</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1066157</t>
+          <t>1064664</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1153994</t>
+          <t>1154342</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1777599</t>
+          <t>1777418</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1867725</t>
+          <t>1872999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2872017</t>
+          <t>2864245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2999301</t>
+          <t>2997803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46985</t>
+          <t>46116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71789</t>
+          <t>71470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68542</t>
+          <t>68273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131838</t>
+          <t>133506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85012</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>110685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114647</t>
+          <t>114916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139834</t>
+          <t>141521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208152</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244396</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130532</t>
+          <t>130950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>167579</t>
+          <t>166142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75009</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110850</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215154</t>
+          <t>216727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267229</t>
+          <t>269224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159886</t>
+          <t>161323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196933</t>
+          <t>196515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297315</t>
+          <t>298145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333156</t>
+          <t>332099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468401</t>
+          <t>466406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>520476</t>
+          <t>518903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75979</t>
+          <t>76878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102930</t>
+          <t>103262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65184</t>
+          <t>64890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>96517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150096</t>
+          <t>151557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191174</t>
+          <t>192419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>82718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110001</t>
+          <t>109102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149847</t>
+          <t>149237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180570</t>
+          <t>180864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240560</t>
+          <t>239315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281638</t>
+          <t>280177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80586</t>
+          <t>81562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111037</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66508</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99751</t>
+          <t>100926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156338</t>
+          <t>155865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198842</t>
+          <t>199889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140949</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171400</t>
+          <t>170424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199577</t>
+          <t>198402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232820</t>
+          <t>232016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>352472</t>
+          <t>351425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394976</t>
+          <t>395449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>55043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78343</t>
+          <t>77500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>45238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69375</t>
+          <t>70310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108499</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139706</t>
+          <t>140947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>52791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74384</t>
+          <t>75248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92795</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118138</t>
+          <t>116932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152755</t>
+          <t>151514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183962</t>
+          <t>184992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61823</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86332</t>
+          <t>86221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33428</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>58405</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102561</t>
+          <t>100981</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137620</t>
+          <t>136361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>69400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93798</t>
+          <t>94197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134981</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159453</t>
+          <t>159742</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210881</t>
+          <t>212140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245940</t>
+          <t>247520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135201</t>
+          <t>136107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171006</t>
+          <t>172166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132473</t>
+          <t>134364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173491</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>282486</t>
+          <t>279432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335719</t>
+          <t>331721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>121058</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158023</t>
+          <t>157117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223528</t>
+          <t>222427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264546</t>
+          <t>262655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>354524</t>
+          <t>358522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>407757</t>
+          <t>410811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190924</t>
+          <t>193708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>234361</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156100</t>
+          <t>156149</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203457</t>
+          <t>201957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>361080</t>
+          <t>358079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>426342</t>
+          <t>427288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>210588</t>
+          <t>208809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>254025</t>
+          <t>251241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>366314</t>
+          <t>367814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>413671</t>
+          <t>413622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588378</t>
+          <t>587432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>653640</t>
+          <t>656641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>857980</t>
+          <t>855290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>945922</t>
+          <t>942040</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>693930</t>
+          <t>693138</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>788550</t>
+          <t>788114</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1575264</t>
+          <t>1582330</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1701824</t>
+          <t>1705488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1000394</t>
+          <t>1004276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1088336</t>
+          <t>1091026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1669726</t>
+          <t>1670162</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1764346</t>
+          <t>1765138</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2702769</t>
+          <t>2699105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2829329</t>
+          <t>2822263</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>39180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67792</t>
+          <t>68267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91641</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82878</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99363</t>
+          <t>97444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>113998</t>
+          <t>131453</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106111</t>
+          <t>124124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>138549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>205640</t>
+          <t>221490</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193397</t>
+          <t>210385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216914</t>
+          <t>232231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>115347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>115347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>115347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145302</t>
+          <t>163304</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145302</t>
+          <t>163304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145302</t>
+          <t>163304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>261189</t>
+          <t>278652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261189</t>
+          <t>278652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>261189</t>
+          <t>278652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>134827</t>
+          <t>143060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112546</t>
+          <t>122858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157882</t>
+          <t>162994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>122029</t>
+          <t>126989</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107931</t>
+          <t>111483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>143245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>256856</t>
+          <t>270049</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230554</t>
+          <t>244893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285318</t>
+          <t>296355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>134177</t>
+          <t>128350</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111122</t>
+          <t>108416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156458</t>
+          <t>148552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>218828</t>
+          <t>236516</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202803</t>
+          <t>220260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232926</t>
+          <t>252022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>353005</t>
+          <t>364867</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>324543</t>
+          <t>338561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>379307</t>
+          <t>390023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>269004</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>269004</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>269004</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>340857</t>
+          <t>363505</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>340857</t>
+          <t>363505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>340857</t>
+          <t>363505</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>609861</t>
+          <t>634916</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>609861</t>
+          <t>634916</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>609861</t>
+          <t>634916</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91782</t>
+          <t>90091</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78898</t>
+          <t>76546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104381</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83726</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72240</t>
+          <t>74730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175507</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158649</t>
+          <t>159661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192816</t>
+          <t>192910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74609</t>
+          <t>75367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87493</t>
+          <t>88912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>143350</t>
+          <t>146030</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131209</t>
+          <t>134464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154836</t>
+          <t>157404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>217960</t>
+          <t>221397</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200651</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234818</t>
+          <t>237931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>166391</t>
+          <t>165458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166391</t>
+          <t>165458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166391</t>
+          <t>165458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227076</t>
+          <t>232134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>227076</t>
+          <t>232134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>227076</t>
+          <t>232134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>393467</t>
+          <t>397592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>393467</t>
+          <t>397592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>393467</t>
+          <t>397592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63227</t>
+          <t>71949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92849</t>
+          <t>103269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>86066</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69887</t>
+          <t>74545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91791</t>
+          <t>98650</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>174980</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141114</t>
+          <t>154858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177293</t>
+          <t>193399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64713</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50882</t>
+          <t>55234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>86554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>134312</t>
+          <t>152825</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123217</t>
+          <t>140241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145121</t>
+          <t>164346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>199025</t>
+          <t>222414</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181445</t>
+          <t>203995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217624</t>
+          <t>242536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>215008</t>
+          <t>238891</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>215008</t>
+          <t>238891</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>215008</t>
+          <t>238891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>358738</t>
+          <t>397394</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>358738</t>
+          <t>397394</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>358738</t>
+          <t>397394</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35523</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>76728</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63036</t>
+          <t>66442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82364</t>
+          <t>85732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33107</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58764</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52101</t>
+          <t>55921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>69881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>91871</t>
+          <t>99398</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82560</t>
+          <t>90394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101888</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>106619</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>106619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>106619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>164924</t>
+          <t>176126</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>164924</t>
+          <t>176126</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164924</t>
+          <t>176126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>79086</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68637</t>
+          <t>67254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91088</t>
+          <t>88748</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>61298</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68298</t>
+          <t>71369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>139872</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>126604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152945</t>
+          <t>155696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43487</t>
+          <t>45875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65938</t>
+          <t>67369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110718</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102356</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>123361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>165357</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152284</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180832</t>
+          <t>184415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>134575</t>
+          <t>134623</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134575</t>
+          <t>134623</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>134575</t>
+          <t>134623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>176396</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>176396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>176396</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>305229</t>
+          <t>311019</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>305229</t>
+          <t>311019</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>305229</t>
+          <t>311019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>158673</t>
+          <t>190427</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137974</t>
+          <t>167054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180210</t>
+          <t>212568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>347820</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221618</t>
+          <t>154222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>192750</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>506493</t>
+          <t>364021</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392210</t>
+          <t>337112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>671417</t>
+          <t>395582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>130121</t>
+          <t>140534</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108584</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150820</t>
+          <t>163907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>189410</t>
+          <t>230234</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63616</t>
+          <t>211078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315612</t>
+          <t>249606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>319531</t>
+          <t>370768</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154607</t>
+          <t>339207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>433814</t>
+          <t>397677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>288794</t>
+          <t>330961</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>288794</t>
+          <t>330961</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>288794</t>
+          <t>330961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>537230</t>
+          <t>403828</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>537230</t>
+          <t>403828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>537230</t>
+          <t>403828</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>826024</t>
+          <t>734789</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>826024</t>
+          <t>734789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>826024</t>
+          <t>734789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>201594</t>
+          <t>224104</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183041</t>
+          <t>201291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219081</t>
+          <t>243321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>175796</t>
+          <t>201590</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159640</t>
+          <t>182729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192255</t>
+          <t>222877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>377390</t>
+          <t>425695</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354763</t>
+          <t>395686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402129</t>
+          <t>452500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>96049</t>
+          <t>115990</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>96773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114602</t>
+          <t>138803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>265760</t>
+          <t>313790</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249301</t>
+          <t>292503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>332651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>361809</t>
+          <t>429779</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>337070</t>
+          <t>402974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384436</t>
+          <t>459788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>297643</t>
+          <t>340094</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>297643</t>
+          <t>340094</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>297643</t>
+          <t>340094</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>739199</t>
+          <t>855474</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>739199</t>
+          <t>855474</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>739199</t>
+          <t>855474</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>757511</t>
+          <t>827195</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>850378</t>
+          <t>916420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>803430</t>
+          <t>772622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1297233</t>
+          <t>847928</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1614534</t>
+          <t>1622520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2133061</t>
+          <t>1743348</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>679057</t>
+          <t>711454</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>630149</t>
+          <t>669484</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>723016</t>
+          <t>758709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1235141</t>
+          <t>1389294</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>880870</t>
+          <t>1352130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1374673</t>
+          <t>1427436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1914198</t>
+          <t>2100749</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1525569</t>
+          <t>2042614</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2044096</t>
+          <t>2163442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
